--- a/incident_report_forms/035_nursing_home_incident_report_form--incident_report_forms.xlsx
+++ b/incident_report_forms/035_nursing_home_incident_report_form--incident_report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'options':_['falls',_'infection',_'medication_error',_'other']}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'options': ['Falls', 'Infection', 'Medication Error', 'Other']}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'other_(specify)':_none}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Other (Specify)': None}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'options':_[]}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'options': []}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'options':_['none',_'alert',_'restless',_'confused',_{'options':_[]}]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'options': ['None', 'Alert', 'Restless', 'Confused', {'options': []}]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'options':_[]}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'options': []}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'options':_['none',_'minor_injury',_'moderate_injury',_'severe_injury',_{'options':_[]},_'none',_'minor_injury',_'moderate_injury',_'severe_injury',_{'options':_[]}]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'options': ['None', 'Minor injury', 'Moderate injury', 'Severe injury', {'options': []}, 'None', 'Minor injury', 'Moderate injury', 'Severe injury', {'options': []}]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'required':_true}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'required': True}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'options':_['none',_'in_review',_'review_complete',_{'options':_[]},_'none',_'in_review',_'review_complete',_{'options':_[]}]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'options': ['None', 'In Review', 'Review Complete', {'options': []}, 'None', 'In Review', 'Review Complete', {'options': []}]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'required':_true}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'required': True}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'options':_['none',_'active',_'inactive',_{'options':_[]},_'none',_'active',_'inactive',_{'options':_[]}]}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'options': ['None', 'Active', 'Inactive', {'options': []}, 'None', 'Active', 'Inactive', {'options': []}]}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'required':_true}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'required': True}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
